--- a/public/file/pegawai/data-pegawai.xlsx
+++ b/public/file/pegawai/data-pegawai.xlsx
@@ -21439,9 +21439,11 @@
         <v>26</v>
       </c>
       <c r="O316" t="s">
-        <v>19</v>
-      </c>
-      <c r="P316"/>
+        <v>235</v>
+      </c>
+      <c r="P316" t="s">
+        <v>1711</v>
+      </c>
     </row>
     <row r="317" spans="1:16">
       <c r="A317">

--- a/public/file/pegawai/data-pegawai.xlsx
+++ b/public/file/pegawai/data-pegawai.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2157">
   <si>
     <t>No</t>
   </si>
@@ -4004,6 +4004,12 @@
   </si>
   <si>
     <t>2000-09-11</t>
+  </si>
+  <si>
+    <t>'4548745484</t>
+  </si>
+  <si>
+    <t>reveh37792@etenx.com</t>
   </si>
   <si>
     <t>'1930885</t>
@@ -18093,19 +18099,21 @@
         <v>26</v>
       </c>
       <c r="O244" t="s">
-        <v>19</v>
-      </c>
-      <c r="P244"/>
+        <v>1329</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1330</v>
+      </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245">
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C245" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="D245" t="s">
         <v>73</v>
@@ -18114,7 +18122,7 @@
         <v>19</v>
       </c>
       <c r="F245" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="G245" t="s">
         <v>1303</v>
@@ -18126,13 +18134,13 @@
         <v>264</v>
       </c>
       <c r="J245" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="K245" t="s">
         <v>34</v>
       </c>
       <c r="L245" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="M245"/>
       <c r="N245" t="s">
@@ -18148,10 +18156,10 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C246" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D246" t="s">
         <v>18</v>
@@ -18166,19 +18174,19 @@
         <v>1303</v>
       </c>
       <c r="H246" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="I246" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="J246" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="K246" t="s">
         <v>426</v>
       </c>
       <c r="L246" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="M246"/>
       <c r="N246" t="s">
@@ -18194,10 +18202,10 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="C247" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D247" t="s">
         <v>73</v>
@@ -18218,13 +18226,13 @@
         <v>1309</v>
       </c>
       <c r="J247" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="K247" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="L247" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="M247"/>
       <c r="N247" t="s">
@@ -18240,10 +18248,10 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C248" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D248" t="s">
         <v>18</v>
@@ -18258,19 +18266,19 @@
         <v>1303</v>
       </c>
       <c r="H248" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="I248" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="J248" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="K248" t="s">
         <v>1257</v>
       </c>
       <c r="L248" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="M248"/>
       <c r="N248" t="s">
@@ -18286,10 +18294,10 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C249" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D249" t="s">
         <v>18</v>
@@ -18298,7 +18306,7 @@
         <v>19</v>
       </c>
       <c r="F249" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="G249" t="s">
         <v>1303</v>
@@ -18310,13 +18318,13 @@
         <v>905</v>
       </c>
       <c r="J249" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="K249" t="s">
         <v>24</v>
       </c>
       <c r="L249" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="M249"/>
       <c r="N249" t="s">
@@ -18332,10 +18340,10 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C250" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="D250" t="s">
         <v>18</v>
@@ -18344,19 +18352,19 @@
         <v>19</v>
       </c>
       <c r="F250" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="G250" t="s">
         <v>1303</v>
       </c>
       <c r="H250" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="I250" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="J250" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="K250" t="s">
         <v>24</v>
@@ -18378,10 +18386,10 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C251" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D251" t="s">
         <v>18</v>
@@ -18402,13 +18410,13 @@
         <v>1020</v>
       </c>
       <c r="J251" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="K251" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="L251" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="M251"/>
       <c r="N251" t="s">
@@ -18424,10 +18432,10 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C252" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D252" t="s">
         <v>18</v>
@@ -18442,19 +18450,19 @@
         <v>1303</v>
       </c>
       <c r="H252" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="I252" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="J252" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="K252" t="s">
         <v>426</v>
       </c>
       <c r="L252" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="M252"/>
       <c r="N252" t="s">
@@ -18470,10 +18478,10 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C253" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="D253" t="s">
         <v>18</v>
@@ -18494,13 +18502,13 @@
         <v>68</v>
       </c>
       <c r="J253" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="K253" t="s">
         <v>53</v>
       </c>
       <c r="L253" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="M253"/>
       <c r="N253" t="s">
@@ -18516,10 +18524,10 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="C254" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D254" t="s">
         <v>73</v>
@@ -18543,10 +18551,10 @@
         <v>1323</v>
       </c>
       <c r="K254" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="L254" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="M254"/>
       <c r="N254" t="s">
@@ -18562,10 +18570,10 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C255" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="D255" t="s">
         <v>18</v>
@@ -18580,19 +18588,19 @@
         <v>1303</v>
       </c>
       <c r="H255" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="I255" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="J255" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="K255" t="s">
         <v>24</v>
       </c>
       <c r="L255" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="M255"/>
       <c r="N255" t="s">
@@ -18608,10 +18616,10 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="C256" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="D256" t="s">
         <v>18</v>
@@ -18632,13 +18640,13 @@
         <v>1020</v>
       </c>
       <c r="J256" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="K256" t="s">
         <v>24</v>
       </c>
       <c r="L256" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="M256"/>
       <c r="N256" t="s">
@@ -18654,10 +18662,10 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C257" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="D257" t="s">
         <v>18</v>
@@ -18678,13 +18686,13 @@
         <v>1026</v>
       </c>
       <c r="J257" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="K257" t="s">
         <v>24</v>
       </c>
       <c r="L257" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="M257"/>
       <c r="N257" t="s">
@@ -18700,10 +18708,10 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="C258" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="D258" t="s">
         <v>18</v>
@@ -18712,10 +18720,10 @@
         <v>19</v>
       </c>
       <c r="F258" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="G258" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H258" t="s">
         <v>1244</v>
@@ -18724,13 +18732,13 @@
         <v>1244</v>
       </c>
       <c r="J258" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="K258" t="s">
         <v>1154</v>
       </c>
       <c r="L258" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="M258"/>
       <c r="N258" t="s">
@@ -18746,10 +18754,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C259" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="D259" t="s">
         <v>18</v>
@@ -18758,25 +18766,25 @@
         <v>19</v>
       </c>
       <c r="F259" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="G259" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H259" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="I259" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J259" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K259" t="s">
         <v>53</v>
       </c>
       <c r="L259" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="M259"/>
       <c r="N259" t="s">
@@ -18792,10 +18800,10 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C260" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D260" t="s">
         <v>18</v>
@@ -18804,10 +18812,10 @@
         <v>19</v>
       </c>
       <c r="F260" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="G260" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H260" t="s">
         <v>949</v>
@@ -18816,13 +18824,13 @@
         <v>949</v>
       </c>
       <c r="J260" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="K260" t="s">
         <v>333</v>
       </c>
       <c r="L260" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="M260"/>
       <c r="N260" t="s">
@@ -18838,37 +18846,37 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="C261" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="D261" t="s">
         <v>18</v>
       </c>
       <c r="E261" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="F261" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="G261" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H261" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="I261" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="J261" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="K261" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="L261" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="M261" t="s">
         <v>151</v>
@@ -18886,10 +18894,10 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="C262" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="D262" t="s">
         <v>18</v>
@@ -18898,10 +18906,10 @@
         <v>19</v>
       </c>
       <c r="F262" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="G262" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H262" t="s">
         <v>74</v>
@@ -18910,13 +18918,13 @@
         <v>74</v>
       </c>
       <c r="J262" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="K262" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="L262" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="M262"/>
       <c r="N262" t="s">
@@ -18932,10 +18940,10 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="C263" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="D263" t="s">
         <v>18</v>
@@ -18944,25 +18952,25 @@
         <v>19</v>
       </c>
       <c r="F263" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="G263" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="H263" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="I263" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="J263" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="K263" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="L263" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="M263"/>
       <c r="N263" t="s">
@@ -18978,10 +18986,10 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C264" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D264" t="s">
         <v>18</v>
@@ -18993,7 +19001,7 @@
         <v>263</v>
       </c>
       <c r="G264" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H264" t="s">
         <v>878</v>
@@ -19002,13 +19010,13 @@
         <v>878</v>
       </c>
       <c r="J264" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="K264" t="s">
         <v>53</v>
       </c>
       <c r="L264" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="M264"/>
       <c r="N264" t="s">
@@ -19024,10 +19032,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="C265" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="D265" t="s">
         <v>18</v>
@@ -19036,10 +19044,10 @@
         <v>19</v>
       </c>
       <c r="F265" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G265" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H265" t="s">
         <v>549</v>
@@ -19048,13 +19056,13 @@
         <v>549</v>
       </c>
       <c r="J265" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K265" t="s">
         <v>34</v>
       </c>
       <c r="L265" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="M265"/>
       <c r="N265" t="s">
@@ -19070,10 +19078,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="C266" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="D266" t="s">
         <v>18</v>
@@ -19082,10 +19090,10 @@
         <v>19</v>
       </c>
       <c r="F266" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G266" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H266" t="s">
         <v>817</v>
@@ -19094,13 +19102,13 @@
         <v>817</v>
       </c>
       <c r="J266" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="K266" t="s">
         <v>76</v>
       </c>
       <c r="L266" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="M266"/>
       <c r="N266" t="s">
@@ -19116,10 +19124,10 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C267" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="D267" t="s">
         <v>18</v>
@@ -19128,10 +19136,10 @@
         <v>19</v>
       </c>
       <c r="F267" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G267" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H267" t="s">
         <v>823</v>
@@ -19146,7 +19154,7 @@
         <v>24</v>
       </c>
       <c r="L267" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="M267"/>
       <c r="N267" t="s">
@@ -19162,37 +19170,37 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C268" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="D268" t="s">
         <v>18</v>
       </c>
       <c r="E268" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F268" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G268" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H268" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I268" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="J268" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="K268" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="L268" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="M268" t="s">
         <v>236</v>
@@ -19210,10 +19218,10 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C269" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D269" t="s">
         <v>18</v>
@@ -19225,22 +19233,22 @@
         <v>44</v>
       </c>
       <c r="G269" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H269" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="I269" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="J269" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="K269" t="s">
         <v>34</v>
       </c>
       <c r="L269" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="M269"/>
       <c r="N269" t="s">
@@ -19256,10 +19264,10 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C270" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="D270" t="s">
         <v>18</v>
@@ -19268,25 +19276,25 @@
         <v>19</v>
       </c>
       <c r="F270" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G270" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H270" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="I270" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J270" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="K270" t="s">
         <v>53</v>
       </c>
       <c r="L270" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="M270"/>
       <c r="N270" t="s">
@@ -19302,10 +19310,10 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C271" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D271" t="s">
         <v>18</v>
@@ -19314,10 +19322,10 @@
         <v>19</v>
       </c>
       <c r="F271" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G271" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H271" t="s">
         <v>74</v>
@@ -19326,13 +19334,13 @@
         <v>74</v>
       </c>
       <c r="J271" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="K271" t="s">
         <v>53</v>
       </c>
       <c r="L271" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="M271"/>
       <c r="N271" t="s">
@@ -19348,10 +19356,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C272" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="D272" t="s">
         <v>18</v>
@@ -19360,19 +19368,19 @@
         <v>19</v>
       </c>
       <c r="F272" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G272" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H272" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="I272" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="J272" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="K272" t="s">
         <v>53</v>
@@ -19394,10 +19402,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C273" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="D273" t="s">
         <v>18</v>
@@ -19406,25 +19414,25 @@
         <v>19</v>
       </c>
       <c r="F273" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G273" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H273" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="I273" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="J273" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="K273" t="s">
         <v>24</v>
       </c>
       <c r="L273" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="M273"/>
       <c r="N273" t="s">
@@ -19440,37 +19448,37 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C274" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="D274" t="s">
         <v>18</v>
       </c>
       <c r="E274" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="F274" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G274" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H274" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="I274" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="J274" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="K274" t="s">
         <v>24</v>
       </c>
       <c r="L274" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="M274" t="s">
         <v>151</v>
@@ -19479,7 +19487,7 @@
         <v>36</v>
       </c>
       <c r="O274" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="P274"/>
     </row>
@@ -19488,10 +19496,10 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C275" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D275" t="s">
         <v>73</v>
@@ -19500,10 +19508,10 @@
         <v>19</v>
       </c>
       <c r="F275" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G275" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H275" t="s">
         <v>752</v>
@@ -19512,13 +19520,13 @@
         <v>752</v>
       </c>
       <c r="J275" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="K275" t="s">
         <v>24</v>
       </c>
       <c r="L275" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="M275"/>
       <c r="N275" t="s">
@@ -19534,10 +19542,10 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C276" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="D276" t="s">
         <v>18</v>
@@ -19546,25 +19554,25 @@
         <v>19</v>
       </c>
       <c r="F276" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G276" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H276" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="I276" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="J276" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="K276" t="s">
         <v>34</v>
       </c>
       <c r="L276" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="M276"/>
       <c r="N276" t="s">
@@ -19580,10 +19588,10 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C277" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="D277" t="s">
         <v>18</v>
@@ -19592,25 +19600,25 @@
         <v>19</v>
       </c>
       <c r="F277" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G277" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H277" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="I277" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="J277" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K277" t="s">
         <v>34</v>
       </c>
       <c r="L277" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="M277" t="s">
         <v>151</v>
@@ -19619,7 +19627,7 @@
         <v>36</v>
       </c>
       <c r="O277" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="P277"/>
     </row>
@@ -19628,10 +19636,10 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="C278" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="D278" t="s">
         <v>73</v>
@@ -19640,25 +19648,25 @@
         <v>19</v>
       </c>
       <c r="F278" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G278" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H278" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="I278" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="J278" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K278" t="s">
         <v>34</v>
       </c>
       <c r="L278" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="M278"/>
       <c r="N278" t="s">
@@ -19674,10 +19682,10 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C279" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D279" t="s">
         <v>18</v>
@@ -19686,34 +19694,34 @@
         <v>19</v>
       </c>
       <c r="F279" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G279" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H279" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I279" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J279" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="K279" t="s">
         <v>53</v>
       </c>
       <c r="L279" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="M279" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="N279" t="s">
         <v>36</v>
       </c>
       <c r="O279" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="P279"/>
     </row>
@@ -19722,22 +19730,22 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C280" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="D280" t="s">
         <v>73</v>
       </c>
       <c r="E280" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="F280" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G280" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H280" t="s">
         <v>1038</v>
@@ -19746,13 +19754,13 @@
         <v>1038</v>
       </c>
       <c r="J280" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="K280" t="s">
         <v>24</v>
       </c>
       <c r="L280" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="M280" t="s">
         <v>151</v>
@@ -19761,7 +19769,7 @@
         <v>36</v>
       </c>
       <c r="O280" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="P280"/>
     </row>
@@ -19770,10 +19778,10 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C281" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="D281" t="s">
         <v>73</v>
@@ -19782,25 +19790,25 @@
         <v>19</v>
       </c>
       <c r="F281" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G281" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="H281" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="I281" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="J281" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="K281" t="s">
         <v>24</v>
       </c>
       <c r="L281" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="M281"/>
       <c r="N281" t="s">
@@ -19816,10 +19824,10 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C282" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="D282" t="s">
         <v>18</v>
@@ -19828,25 +19836,25 @@
         <v>19</v>
       </c>
       <c r="F282" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="G282" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="H282" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="I282" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="J282" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="K282" t="s">
         <v>53</v>
       </c>
       <c r="L282" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="M282"/>
       <c r="N282" t="s">
@@ -19862,10 +19870,10 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C283" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D283" t="s">
         <v>73</v>
@@ -19874,25 +19882,25 @@
         <v>19</v>
       </c>
       <c r="F283" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="G283" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="H283" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="I283" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="J283" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="K283" t="s">
         <v>24</v>
       </c>
       <c r="L283" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="M283"/>
       <c r="N283" t="s">
@@ -19908,10 +19916,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="C284" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D284" t="s">
         <v>73</v>
@@ -19920,25 +19928,25 @@
         <v>19</v>
       </c>
       <c r="F284" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="G284" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="H284" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="I284" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="J284" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="K284" t="s">
         <v>53</v>
       </c>
       <c r="L284" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="M284"/>
       <c r="N284" t="s">
@@ -19954,37 +19962,37 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="C285" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="D285" t="s">
         <v>18</v>
       </c>
       <c r="E285" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F285" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="G285" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H285" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="I285" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J285" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="K285" t="s">
         <v>426</v>
       </c>
       <c r="L285" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="M285" t="s">
         <v>236</v>
@@ -20002,10 +20010,10 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C286" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D286" t="s">
         <v>73</v>
@@ -20014,25 +20022,25 @@
         <v>19</v>
       </c>
       <c r="F286" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="G286" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H286" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="I286" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="J286" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="K286" t="s">
         <v>53</v>
       </c>
       <c r="L286" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="M286"/>
       <c r="N286" t="s">
@@ -20048,10 +20056,10 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C287" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D287" t="s">
         <v>73</v>
@@ -20060,10 +20068,10 @@
         <v>19</v>
       </c>
       <c r="F287" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G287" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H287" t="s">
         <v>74</v>
@@ -20072,13 +20080,13 @@
         <v>74</v>
       </c>
       <c r="J287" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="K287" t="s">
         <v>1016</v>
       </c>
       <c r="L287" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="M287"/>
       <c r="N287" t="s">
@@ -20094,10 +20102,10 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C288" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="D288" t="s">
         <v>73</v>
@@ -20106,25 +20114,25 @@
         <v>19</v>
       </c>
       <c r="F288" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="G288" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H288" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I288" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="J288" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K288" t="s">
         <v>1154</v>
       </c>
       <c r="L288" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M288"/>
       <c r="N288" t="s">
@@ -20140,10 +20148,10 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="C289" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="D289" t="s">
         <v>18</v>
@@ -20152,25 +20160,25 @@
         <v>19</v>
       </c>
       <c r="F289" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="G289" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H289" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="I289" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="J289" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="K289" t="s">
         <v>24</v>
       </c>
       <c r="L289" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="M289"/>
       <c r="N289" t="s">
@@ -20186,10 +20194,10 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C290" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="D290" t="s">
         <v>73</v>
@@ -20198,25 +20206,25 @@
         <v>19</v>
       </c>
       <c r="F290" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="G290" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H290" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="I290" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="J290" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="K290" t="s">
         <v>53</v>
       </c>
       <c r="L290" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="M290"/>
       <c r="N290" t="s">
@@ -20232,10 +20240,10 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="C291" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="D291" t="s">
         <v>18</v>
@@ -20244,25 +20252,25 @@
         <v>19</v>
       </c>
       <c r="F291" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="G291" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H291" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I291" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="J291" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="K291" t="s">
         <v>53</v>
       </c>
       <c r="L291" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="M291"/>
       <c r="N291" t="s">
@@ -20278,10 +20286,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C292" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="D292" t="s">
         <v>18</v>
@@ -20290,10 +20298,10 @@
         <v>19</v>
       </c>
       <c r="F292" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="G292" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H292" t="s">
         <v>74</v>
@@ -20302,7 +20310,7 @@
         <v>74</v>
       </c>
       <c r="J292" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="K292" t="s">
         <v>53</v>
@@ -20324,10 +20332,10 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="C293" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="D293" t="s">
         <v>73</v>
@@ -20336,25 +20344,25 @@
         <v>19</v>
       </c>
       <c r="F293" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="G293" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H293" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="I293" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="J293" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="K293" t="s">
         <v>53</v>
       </c>
       <c r="L293" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="M293"/>
       <c r="N293" t="s">
@@ -20370,10 +20378,10 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C294" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D294" t="s">
         <v>18</v>
@@ -20382,25 +20390,25 @@
         <v>19</v>
       </c>
       <c r="F294" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G294" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H294" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="I294" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="J294" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="K294" t="s">
         <v>53</v>
       </c>
       <c r="L294" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="M294"/>
       <c r="N294" t="s">
@@ -20416,10 +20424,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="C295" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D295" t="s">
         <v>18</v>
@@ -20428,25 +20436,25 @@
         <v>19</v>
       </c>
       <c r="F295" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="G295" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H295" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="I295" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="J295" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="K295" t="s">
         <v>812</v>
       </c>
       <c r="L295" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M295"/>
       <c r="N295" t="s">
@@ -20462,10 +20470,10 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C296" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D296" t="s">
         <v>18</v>
@@ -20474,10 +20482,10 @@
         <v>19</v>
       </c>
       <c r="F296" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="G296" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H296" t="s">
         <v>411</v>
@@ -20486,13 +20494,13 @@
         <v>411</v>
       </c>
       <c r="J296" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="K296" t="s">
         <v>53</v>
       </c>
       <c r="L296" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="M296"/>
       <c r="N296" t="s">
@@ -20508,10 +20516,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="C297" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="D297" t="s">
         <v>18</v>
@@ -20520,25 +20528,25 @@
         <v>19</v>
       </c>
       <c r="F297" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="G297" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="H297" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="I297" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="J297" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="K297" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="L297" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="M297"/>
       <c r="N297" t="s">
@@ -20554,10 +20562,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C298" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D298" t="s">
         <v>18</v>
@@ -20569,7 +20577,7 @@
         <v>802</v>
       </c>
       <c r="G298" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H298" t="s">
         <v>74</v>
@@ -20578,13 +20586,13 @@
         <v>74</v>
       </c>
       <c r="J298" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="K298" t="s">
         <v>34</v>
       </c>
       <c r="L298" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="M298"/>
       <c r="N298" t="s">
@@ -20600,37 +20608,37 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="C299" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="D299" t="s">
         <v>18</v>
       </c>
       <c r="E299" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="F299" t="s">
         <v>802</v>
       </c>
       <c r="G299" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H299" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="I299" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="J299" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="K299" t="s">
         <v>53</v>
       </c>
       <c r="L299" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="M299" t="s">
         <v>236</v>
@@ -20639,7 +20647,7 @@
         <v>26</v>
       </c>
       <c r="O299" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="P299"/>
     </row>
@@ -20648,10 +20656,10 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C300" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D300" t="s">
         <v>18</v>
@@ -20663,22 +20671,22 @@
         <v>802</v>
       </c>
       <c r="G300" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H300" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="I300" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="J300" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K300" t="s">
         <v>24</v>
       </c>
       <c r="L300" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="M300" t="s">
         <v>236</v>
@@ -20687,7 +20695,7 @@
         <v>36</v>
       </c>
       <c r="O300" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="P300"/>
     </row>
@@ -20696,10 +20704,10 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C301" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="D301" t="s">
         <v>18</v>
@@ -20711,22 +20719,22 @@
         <v>802</v>
       </c>
       <c r="G301" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H301" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="I301" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="J301" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="K301" t="s">
         <v>34</v>
       </c>
       <c r="L301" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="M301" t="s">
         <v>151</v>
@@ -20744,10 +20752,10 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="C302" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="D302" t="s">
         <v>18</v>
@@ -20759,7 +20767,7 @@
         <v>315</v>
       </c>
       <c r="G302" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H302" t="s">
         <v>949</v>
@@ -20768,13 +20776,13 @@
         <v>949</v>
       </c>
       <c r="J302" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="K302" t="s">
         <v>24</v>
       </c>
       <c r="L302" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="M302" t="s">
         <v>151</v>
@@ -20783,7 +20791,7 @@
         <v>26</v>
       </c>
       <c r="O302" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="P302"/>
     </row>
@@ -20792,10 +20800,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="C303" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="D303" t="s">
         <v>18</v>
@@ -20807,22 +20815,22 @@
         <v>802</v>
       </c>
       <c r="G303" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H303" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="I303" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="J303" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="K303" t="s">
         <v>34</v>
       </c>
       <c r="L303" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="M303"/>
       <c r="N303" t="s">
@@ -20838,10 +20846,10 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="C304" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="D304" t="s">
         <v>18</v>
@@ -20853,22 +20861,22 @@
         <v>155</v>
       </c>
       <c r="G304" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H304" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="I304" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="J304" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="K304" t="s">
         <v>53</v>
       </c>
       <c r="L304" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="M304"/>
       <c r="N304" t="s">
@@ -20884,10 +20892,10 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="C305" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="D305" t="s">
         <v>18</v>
@@ -20899,22 +20907,22 @@
         <v>802</v>
       </c>
       <c r="G305" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H305" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="I305" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="J305" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="K305" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="L305" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="M305"/>
       <c r="N305" t="s">
@@ -20930,37 +20938,37 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="C306" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="D306" t="s">
         <v>73</v>
       </c>
       <c r="E306" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="F306" t="s">
         <v>802</v>
       </c>
       <c r="G306" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H306" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="I306" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="J306" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="K306" t="s">
         <v>333</v>
       </c>
       <c r="L306" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="M306" t="s">
         <v>151</v>
@@ -20969,7 +20977,7 @@
         <v>26</v>
       </c>
       <c r="O306" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="P306"/>
     </row>
@@ -20978,22 +20986,22 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="C307" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="D307" t="s">
         <v>18</v>
       </c>
       <c r="E307" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="F307" t="s">
         <v>802</v>
       </c>
       <c r="G307" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H307" t="s">
         <v>949</v>
@@ -21002,13 +21010,13 @@
         <v>949</v>
       </c>
       <c r="J307" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="K307" t="s">
         <v>24</v>
       </c>
       <c r="L307" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="M307" t="s">
         <v>151</v>
@@ -21017,7 +21025,7 @@
         <v>26</v>
       </c>
       <c r="O307" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="P307"/>
     </row>
@@ -21026,10 +21034,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="C308" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="D308" t="s">
         <v>18</v>
@@ -21041,22 +21049,22 @@
         <v>802</v>
       </c>
       <c r="G308" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H308" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="I308" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="J308" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="K308" t="s">
         <v>53</v>
       </c>
       <c r="L308" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="M308"/>
       <c r="N308" t="s">
@@ -21072,22 +21080,22 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C309" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="D309" t="s">
         <v>18</v>
       </c>
       <c r="E309" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="F309" t="s">
         <v>802</v>
       </c>
       <c r="G309" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H309" t="s">
         <v>949</v>
@@ -21096,13 +21104,13 @@
         <v>949</v>
       </c>
       <c r="J309" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="K309" t="s">
         <v>24</v>
       </c>
       <c r="L309" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="M309" t="s">
         <v>151</v>
@@ -21111,7 +21119,7 @@
         <v>36</v>
       </c>
       <c r="O309" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="P309"/>
     </row>
@@ -21120,10 +21128,10 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="C310" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="D310" t="s">
         <v>18</v>
@@ -21135,22 +21143,22 @@
         <v>802</v>
       </c>
       <c r="G310" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H310" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="I310" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="J310" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="K310" t="s">
         <v>951</v>
       </c>
       <c r="L310" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="M310"/>
       <c r="N310" t="s">
@@ -21166,37 +21174,37 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C311" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="D311" t="s">
         <v>18</v>
       </c>
       <c r="E311" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="F311" t="s">
         <v>802</v>
       </c>
       <c r="G311" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H311" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="I311" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="J311" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="K311" t="s">
         <v>53</v>
       </c>
       <c r="L311" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="M311" t="s">
         <v>151</v>
@@ -21205,7 +21213,7 @@
         <v>26</v>
       </c>
       <c r="O311" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="P311"/>
     </row>
@@ -21214,10 +21222,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="C312" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="D312" t="s">
         <v>73</v>
@@ -21229,7 +21237,7 @@
         <v>802</v>
       </c>
       <c r="G312" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H312" t="s">
         <v>1104</v>
@@ -21238,13 +21246,13 @@
         <v>1104</v>
       </c>
       <c r="J312" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="K312" t="s">
         <v>53</v>
       </c>
       <c r="L312" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="M312"/>
       <c r="N312" t="s">
@@ -21260,37 +21268,37 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="C313" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="D313" t="s">
         <v>18</v>
       </c>
       <c r="E313" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="F313" t="s">
         <v>802</v>
       </c>
       <c r="G313" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H313" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="I313" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="J313" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="K313" t="s">
         <v>53</v>
       </c>
       <c r="L313" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="M313" t="s">
         <v>151</v>
@@ -21299,7 +21307,7 @@
         <v>36</v>
       </c>
       <c r="O313" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="P313"/>
     </row>
@@ -21308,10 +21316,10 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="C314" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="D314" t="s">
         <v>18</v>
@@ -21323,22 +21331,22 @@
         <v>802</v>
       </c>
       <c r="G314" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="H314" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="I314" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="J314" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K314" t="s">
         <v>53</v>
       </c>
       <c r="L314" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="M314" t="s">
         <v>236</v>
@@ -21347,7 +21355,7 @@
         <v>26</v>
       </c>
       <c r="O314" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="P314" t="s">
         <v>28</v>
@@ -21358,10 +21366,10 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="C315" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="D315" t="s">
         <v>18</v>
@@ -21370,25 +21378,25 @@
         <v>19</v>
       </c>
       <c r="F315" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="G315" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="H315" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I315" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="J315" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="K315" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="L315" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="M315"/>
       <c r="N315" t="s">
@@ -21404,10 +21412,10 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C316" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="D316" t="s">
         <v>18</v>
@@ -21419,7 +21427,7 @@
         <v>20</v>
       </c>
       <c r="G316" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H316" t="s">
         <v>380</v>
@@ -21428,13 +21436,13 @@
         <v>380</v>
       </c>
       <c r="J316" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="K316" t="s">
         <v>716</v>
       </c>
       <c r="L316" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="M316"/>
       <c r="N316" t="s">
@@ -21452,10 +21460,10 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="C317" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="D317" t="s">
         <v>18</v>
@@ -21467,7 +21475,7 @@
         <v>20</v>
       </c>
       <c r="G317" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H317" t="s">
         <v>804</v>
@@ -21476,13 +21484,13 @@
         <v>804</v>
       </c>
       <c r="J317" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="K317" t="s">
         <v>333</v>
       </c>
       <c r="L317" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="M317"/>
       <c r="N317" t="s">
@@ -21498,10 +21506,10 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="C318" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="D318" t="s">
         <v>18</v>
@@ -21513,22 +21521,22 @@
         <v>20</v>
       </c>
       <c r="G318" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H318" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="I318" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="J318" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="K318" t="s">
         <v>34</v>
       </c>
       <c r="L318" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="M318"/>
       <c r="N318" t="s">
@@ -21544,10 +21552,10 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C319" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="D319" t="s">
         <v>18</v>
@@ -21559,22 +21567,22 @@
         <v>263</v>
       </c>
       <c r="G319" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H319" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="I319" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="J319" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="K319" t="s">
         <v>1016</v>
       </c>
       <c r="L319" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="M319"/>
       <c r="N319" t="s">
@@ -21590,10 +21598,10 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="C320" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="D320" t="s">
         <v>18</v>
@@ -21605,22 +21613,22 @@
         <v>20</v>
       </c>
       <c r="G320" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H320" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="I320" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="J320" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="K320" t="s">
         <v>34</v>
       </c>
       <c r="L320" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="M320"/>
       <c r="N320" t="s">
@@ -21636,10 +21644,10 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C321" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D321" t="s">
         <v>18</v>
@@ -21651,7 +21659,7 @@
         <v>20</v>
       </c>
       <c r="G321" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H321" t="s">
         <v>39</v>
@@ -21660,13 +21668,13 @@
         <v>39</v>
       </c>
       <c r="J321" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="K321" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L321" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="M321"/>
       <c r="N321" t="s">
@@ -21682,10 +21690,10 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="C322" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="D322" t="s">
         <v>18</v>
@@ -21697,22 +21705,22 @@
         <v>20</v>
       </c>
       <c r="G322" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H322" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="I322" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="J322" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="K322" t="s">
         <v>24</v>
       </c>
       <c r="L322" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="M322"/>
       <c r="N322" t="s">
@@ -21728,10 +21736,10 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="C323" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="D323" t="s">
         <v>18</v>
@@ -21743,7 +21751,7 @@
         <v>20</v>
       </c>
       <c r="G323" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H323" t="s">
         <v>57</v>
@@ -21752,13 +21760,13 @@
         <v>57</v>
       </c>
       <c r="J323" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="K323" t="s">
         <v>192</v>
       </c>
       <c r="L323" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="M323"/>
       <c r="N323" t="s">
@@ -21774,10 +21782,10 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="C324" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="D324" t="s">
         <v>18</v>
@@ -21789,22 +21797,22 @@
         <v>20</v>
       </c>
       <c r="G324" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="H324" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="I324" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="J324" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="K324" t="s">
         <v>192</v>
       </c>
       <c r="L324" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="M324"/>
       <c r="N324" t="s">
@@ -21820,10 +21828,10 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="C325" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="D325" t="s">
         <v>18</v>
@@ -21835,7 +21843,7 @@
         <v>20</v>
       </c>
       <c r="G325" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H325" t="s">
         <v>80</v>
@@ -21844,13 +21852,13 @@
         <v>80</v>
       </c>
       <c r="J325" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="K325" t="s">
         <v>53</v>
       </c>
       <c r="L325" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="M325"/>
       <c r="N325" t="s">
@@ -21866,10 +21874,10 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="C326" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="D326" t="s">
         <v>18</v>
@@ -21881,7 +21889,7 @@
         <v>20</v>
       </c>
       <c r="G326" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H326" t="s">
         <v>270</v>
@@ -21890,13 +21898,13 @@
         <v>270</v>
       </c>
       <c r="J326" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="K326" t="s">
         <v>53</v>
       </c>
       <c r="L326" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="M326"/>
       <c r="N326" t="s">
@@ -21912,10 +21920,10 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="C327" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D327" t="s">
         <v>18</v>
@@ -21927,22 +21935,22 @@
         <v>31</v>
       </c>
       <c r="G327" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H327" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="I327" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="J327" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="K327" t="s">
         <v>1016</v>
       </c>
       <c r="L327" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="M327"/>
       <c r="N327" t="s">
@@ -21958,10 +21966,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="C328" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="D328" t="s">
         <v>18</v>
@@ -21973,7 +21981,7 @@
         <v>263</v>
       </c>
       <c r="G328" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H328" t="s">
         <v>57</v>
@@ -21982,13 +21990,13 @@
         <v>57</v>
       </c>
       <c r="J328" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="K328" t="s">
         <v>34</v>
       </c>
       <c r="L328" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="M328"/>
       <c r="N328" t="s">
@@ -22004,10 +22012,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="C329" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D329" t="s">
         <v>18</v>
@@ -22019,7 +22027,7 @@
         <v>20</v>
       </c>
       <c r="G329" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H329" t="s">
         <v>57</v>
@@ -22028,13 +22036,13 @@
         <v>57</v>
       </c>
       <c r="J329" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="K329" t="s">
         <v>24</v>
       </c>
       <c r="L329" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="M329"/>
       <c r="N329" t="s">
@@ -22050,10 +22058,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C330" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D330" t="s">
         <v>18</v>
@@ -22065,7 +22073,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H330" t="s">
         <v>57</v>
@@ -22074,13 +22082,13 @@
         <v>57</v>
       </c>
       <c r="J330" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="K330" t="s">
         <v>34</v>
       </c>
       <c r="L330" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="M330"/>
       <c r="N330" t="s">
@@ -22096,10 +22104,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="C331" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="D331" t="s">
         <v>18</v>
@@ -22111,22 +22119,22 @@
         <v>20</v>
       </c>
       <c r="G331" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H331" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="I331" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="J331" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="K331" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="L331" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="M331"/>
       <c r="N331" t="s">
@@ -22142,10 +22150,10 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C332" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D332" t="s">
         <v>18</v>
@@ -22154,25 +22162,25 @@
         <v>19</v>
       </c>
       <c r="F332" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="G332" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H332" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="I332" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="J332" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="K332" t="s">
         <v>53</v>
       </c>
       <c r="L332" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="M332" t="s">
         <v>151</v>
@@ -22181,7 +22189,7 @@
         <v>36</v>
       </c>
       <c r="O332" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="P332"/>
     </row>
@@ -22190,10 +22198,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="C333" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="D333" t="s">
         <v>18</v>
@@ -22205,7 +22213,7 @@
         <v>31</v>
       </c>
       <c r="G333" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H333" t="s">
         <v>1010</v>
@@ -22214,13 +22222,13 @@
         <v>1010</v>
       </c>
       <c r="J333" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="K333" t="s">
         <v>333</v>
       </c>
       <c r="L333" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="M333"/>
       <c r="N333" t="s">
@@ -22236,10 +22244,10 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="C334" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D334" t="s">
         <v>18</v>
@@ -22251,7 +22259,7 @@
         <v>20</v>
       </c>
       <c r="G334" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H334" t="s">
         <v>275</v>
@@ -22260,13 +22268,13 @@
         <v>275</v>
       </c>
       <c r="J334" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="K334" t="s">
         <v>59</v>
       </c>
       <c r="L334" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="M334"/>
       <c r="N334" t="s">
@@ -22282,10 +22290,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="C335" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="D335" t="s">
         <v>18</v>
@@ -22297,22 +22305,22 @@
         <v>1087</v>
       </c>
       <c r="G335" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H335" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="I335" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="J335" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="K335" t="s">
         <v>76</v>
       </c>
       <c r="L335" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="M335"/>
       <c r="N335" t="s">
@@ -22328,10 +22336,10 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C336" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="D336" t="s">
         <v>18</v>
@@ -22343,22 +22351,22 @@
         <v>20</v>
       </c>
       <c r="G336" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H336" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="I336" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="J336" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="K336" t="s">
         <v>59</v>
       </c>
       <c r="L336" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="M336"/>
       <c r="N336" t="s">
@@ -22374,37 +22382,37 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="C337" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="D337" t="s">
         <v>18</v>
       </c>
       <c r="E337" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="F337" t="s">
         <v>31</v>
       </c>
       <c r="G337" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H337" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="I337" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="J337" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="K337" t="s">
         <v>1016</v>
       </c>
       <c r="L337" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="M337" t="s">
         <v>236</v>
@@ -22413,7 +22421,7 @@
         <v>26</v>
       </c>
       <c r="O337" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="P337"/>
     </row>
@@ -22422,10 +22430,10 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C338" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="D338" t="s">
         <v>18</v>
@@ -22437,22 +22445,22 @@
         <v>20</v>
       </c>
       <c r="G338" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H338" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="I338" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="J338" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="K338" t="s">
         <v>333</v>
       </c>
       <c r="L338" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="M338"/>
       <c r="N338" t="s">
@@ -22468,10 +22476,10 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="C339" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="D339" t="s">
         <v>18</v>
@@ -22480,10 +22488,10 @@
         <v>19</v>
       </c>
       <c r="F339" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="G339" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H339" t="s">
         <v>348</v>
@@ -22492,13 +22500,13 @@
         <v>348</v>
       </c>
       <c r="J339" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="K339" t="s">
         <v>34</v>
       </c>
       <c r="L339" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="M339"/>
       <c r="N339" t="s">
@@ -22514,10 +22522,10 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="C340" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="D340" t="s">
         <v>18</v>
@@ -22529,7 +22537,7 @@
         <v>248</v>
       </c>
       <c r="G340" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H340" t="s">
         <v>1010</v>
@@ -22538,13 +22546,13 @@
         <v>1010</v>
       </c>
       <c r="J340" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="K340" t="s">
         <v>53</v>
       </c>
       <c r="L340" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="M340"/>
       <c r="N340" t="s">
@@ -22560,10 +22568,10 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="C341" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="D341" t="s">
         <v>18</v>
@@ -22575,22 +22583,22 @@
         <v>20</v>
       </c>
       <c r="G341" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H341" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="I341" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="J341" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="K341" t="s">
         <v>53</v>
       </c>
       <c r="L341" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="M341"/>
       <c r="N341" t="s">
@@ -22606,10 +22614,10 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="C342" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="D342" t="s">
         <v>18</v>
@@ -22621,7 +22629,7 @@
         <v>20</v>
       </c>
       <c r="G342" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H342" t="s">
         <v>511</v>
@@ -22630,13 +22638,13 @@
         <v>511</v>
       </c>
       <c r="J342" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="K342" t="s">
         <v>53</v>
       </c>
       <c r="L342" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="M342"/>
       <c r="N342" t="s">
@@ -22652,10 +22660,10 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="C343" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="D343" t="s">
         <v>18</v>
@@ -22667,22 +22675,22 @@
         <v>20</v>
       </c>
       <c r="G343" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H343" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="I343" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="J343" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="K343" t="s">
         <v>53</v>
       </c>
       <c r="L343" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="M343"/>
       <c r="N343" t="s">
@@ -22698,10 +22706,10 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="C344" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D344" t="s">
         <v>18</v>
@@ -22713,22 +22721,22 @@
         <v>44</v>
       </c>
       <c r="G344" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H344" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="I344" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="J344" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="K344" t="s">
         <v>1016</v>
       </c>
       <c r="L344" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="M344"/>
       <c r="N344" t="s">
@@ -22744,10 +22752,10 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="C345" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="D345" t="s">
         <v>18</v>
@@ -22759,22 +22767,22 @@
         <v>31</v>
       </c>
       <c r="G345" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H345" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="I345" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="J345" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="K345" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="L345" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="M345"/>
       <c r="N345" t="s">
@@ -22790,10 +22798,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="C346" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="D346" t="s">
         <v>18</v>
@@ -22802,25 +22810,25 @@
         <v>19</v>
       </c>
       <c r="F346" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="G346" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H346" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="I346" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="J346" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="K346" t="s">
         <v>53</v>
       </c>
       <c r="L346" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="M346"/>
       <c r="N346" t="s">
@@ -22836,10 +22844,10 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C347" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D347" t="s">
         <v>18</v>
@@ -22851,7 +22859,7 @@
         <v>20</v>
       </c>
       <c r="G347" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H347" t="s">
         <v>895</v>
@@ -22860,13 +22868,13 @@
         <v>895</v>
       </c>
       <c r="J347" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="K347" t="s">
         <v>874</v>
       </c>
       <c r="L347" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="M347"/>
       <c r="N347" t="s">
@@ -22882,10 +22890,10 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="C348" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="D348" t="s">
         <v>18</v>
@@ -22897,22 +22905,22 @@
         <v>20</v>
       </c>
       <c r="G348" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H348" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="I348" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="J348" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="K348" t="s">
         <v>53</v>
       </c>
       <c r="L348" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="M348"/>
       <c r="N348" t="s">
@@ -22928,10 +22936,10 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="C349" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="D349" t="s">
         <v>18</v>
@@ -22943,7 +22951,7 @@
         <v>31</v>
       </c>
       <c r="G349" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H349" t="s">
         <v>878</v>
@@ -22952,13 +22960,13 @@
         <v>878</v>
       </c>
       <c r="J349" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="K349" t="s">
         <v>47</v>
       </c>
       <c r="L349" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="M349"/>
       <c r="N349" t="s">
@@ -22974,10 +22982,10 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="C350" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D350" t="s">
         <v>18</v>
@@ -22989,7 +22997,7 @@
         <v>20</v>
       </c>
       <c r="G350" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H350" t="s">
         <v>1038</v>
@@ -22998,13 +23006,13 @@
         <v>1038</v>
       </c>
       <c r="J350" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="K350" t="s">
         <v>664</v>
       </c>
       <c r="L350" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="M350"/>
       <c r="N350" t="s">
@@ -23020,10 +23028,10 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="C351" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="D351" t="s">
         <v>18</v>
@@ -23035,7 +23043,7 @@
         <v>248</v>
       </c>
       <c r="G351" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H351" t="s">
         <v>249</v>
@@ -23044,13 +23052,13 @@
         <v>249</v>
       </c>
       <c r="J351" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="K351" t="s">
         <v>536</v>
       </c>
       <c r="L351" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="M351"/>
       <c r="N351" t="s">
@@ -23066,10 +23074,10 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="C352" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="D352" t="s">
         <v>18</v>
@@ -23081,22 +23089,22 @@
         <v>20</v>
       </c>
       <c r="G352" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H352" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="I352" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="J352" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="K352" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="L352" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="M352"/>
       <c r="N352" t="s">
@@ -23112,10 +23120,10 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="C353" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="D353" t="s">
         <v>18</v>
@@ -23127,22 +23135,22 @@
         <v>491</v>
       </c>
       <c r="G353" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="H353" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="I353" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="J353" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="K353" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="L353" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="M353"/>
       <c r="N353" t="s">
@@ -23158,37 +23166,37 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D354" t="s">
+        <v>18</v>
+      </c>
+      <c r="E354" t="s">
+        <v>19</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G354" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H354" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I354" t="s">
+        <v>1905</v>
+      </c>
+      <c r="J354" t="s">
+        <v>1906</v>
+      </c>
+      <c r="K354" t="s">
         <v>1899</v>
       </c>
-      <c r="C354" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D354" t="s">
-        <v>18</v>
-      </c>
-      <c r="E354" t="s">
-        <v>19</v>
-      </c>
-      <c r="F354" t="s">
-        <v>1901</v>
-      </c>
-      <c r="G354" t="s">
-        <v>1902</v>
-      </c>
-      <c r="H354" t="s">
-        <v>1903</v>
-      </c>
-      <c r="I354" t="s">
-        <v>1903</v>
-      </c>
-      <c r="J354" t="s">
-        <v>1904</v>
-      </c>
-      <c r="K354" t="s">
-        <v>1897</v>
-      </c>
       <c r="L354" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="M354"/>
       <c r="N354" t="s">
@@ -23204,10 +23212,10 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C355" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D355" t="s">
         <v>18</v>
@@ -23216,25 +23224,25 @@
         <v>19</v>
       </c>
       <c r="F355" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="G355" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H355" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="I355" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="J355" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="K355" t="s">
         <v>34</v>
       </c>
       <c r="L355" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="M355"/>
       <c r="N355" t="s">
@@ -23250,10 +23258,10 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="C356" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="D356" t="s">
         <v>73</v>
@@ -23262,10 +23270,10 @@
         <v>19</v>
       </c>
       <c r="F356" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="G356" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H356" t="s">
         <v>817</v>
@@ -23274,13 +23282,13 @@
         <v>817</v>
       </c>
       <c r="J356" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="K356" t="s">
         <v>34</v>
       </c>
       <c r="L356" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="M356"/>
       <c r="N356" t="s">
@@ -23296,10 +23304,10 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C357" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="D357" t="s">
         <v>73</v>
@@ -23308,10 +23316,10 @@
         <v>19</v>
       </c>
       <c r="F357" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="G357" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H357" t="s">
         <v>1271</v>
@@ -23320,13 +23328,13 @@
         <v>1271</v>
       </c>
       <c r="J357" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="K357" t="s">
         <v>53</v>
       </c>
       <c r="L357" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="M357"/>
       <c r="N357" t="s">
@@ -23342,10 +23350,10 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C358" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="D358" t="s">
         <v>18</v>
@@ -23354,10 +23362,10 @@
         <v>19</v>
       </c>
       <c r="F358" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="G358" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H358" t="s">
         <v>1271</v>
@@ -23366,13 +23374,13 @@
         <v>1271</v>
       </c>
       <c r="J358" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="K358" t="s">
         <v>471</v>
       </c>
       <c r="L358" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="M358"/>
       <c r="N358" t="s">
@@ -23388,10 +23396,10 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C359" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="D359" t="s">
         <v>18</v>
@@ -23400,25 +23408,25 @@
         <v>19</v>
       </c>
       <c r="F359" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="G359" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H359" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="I359" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="J359" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="K359" t="s">
         <v>53</v>
       </c>
       <c r="L359" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="M359"/>
       <c r="N359" t="s">
@@ -23434,10 +23442,10 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="C360" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="D360" t="s">
         <v>18</v>
@@ -23449,7 +23457,7 @@
         <v>263</v>
       </c>
       <c r="G360" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H360" t="s">
         <v>74</v>
@@ -23458,13 +23466,13 @@
         <v>74</v>
       </c>
       <c r="J360" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="K360" t="s">
         <v>1016</v>
       </c>
       <c r="L360" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="M360"/>
       <c r="N360" t="s">
@@ -23480,37 +23488,37 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="C361" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="D361" t="s">
         <v>18</v>
       </c>
       <c r="E361" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="F361" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="G361" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="H361" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="I361" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J361" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="K361" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="L361" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="M361"/>
       <c r="N361" t="s">
@@ -23526,10 +23534,10 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C362" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="D362" t="s">
         <v>18</v>
@@ -23541,7 +23549,7 @@
         <v>20</v>
       </c>
       <c r="G362" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H362" t="s">
         <v>57</v>
@@ -23550,13 +23558,13 @@
         <v>57</v>
       </c>
       <c r="J362" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="K362" t="s">
         <v>53</v>
       </c>
       <c r="L362" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="M362"/>
       <c r="N362" t="s">
@@ -23572,10 +23580,10 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="C363" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="D363" t="s">
         <v>18</v>
@@ -23587,7 +23595,7 @@
         <v>20</v>
       </c>
       <c r="G363" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H363" t="s">
         <v>157</v>
@@ -23596,13 +23604,13 @@
         <v>157</v>
       </c>
       <c r="J363" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="K363" t="s">
         <v>53</v>
       </c>
       <c r="L363" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="M363"/>
       <c r="N363" t="s">
@@ -23618,10 +23626,10 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="C364" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="D364" t="s">
         <v>18</v>
@@ -23633,7 +23641,7 @@
         <v>248</v>
       </c>
       <c r="G364" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H364" t="s">
         <v>932</v>
@@ -23642,13 +23650,13 @@
         <v>932</v>
       </c>
       <c r="J364" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="K364" t="s">
         <v>24</v>
       </c>
       <c r="L364" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="M364"/>
       <c r="N364" t="s">
@@ -23664,10 +23672,10 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="C365" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="D365" t="s">
         <v>18</v>
@@ -23679,7 +23687,7 @@
         <v>20</v>
       </c>
       <c r="G365" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H365" t="s">
         <v>214</v>
@@ -23688,13 +23696,13 @@
         <v>214</v>
       </c>
       <c r="J365" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="K365" t="s">
         <v>24</v>
       </c>
       <c r="L365" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="M365"/>
       <c r="N365" t="s">
@@ -23710,10 +23718,10 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C366" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D366" t="s">
         <v>18</v>
@@ -23725,22 +23733,22 @@
         <v>20</v>
       </c>
       <c r="G366" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H366" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="I366" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="J366" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="K366" t="s">
         <v>536</v>
       </c>
       <c r="L366" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="M366"/>
       <c r="N366" t="s">
@@ -23756,10 +23764,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="C367" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="D367" t="s">
         <v>18</v>
@@ -23771,22 +23779,22 @@
         <v>20</v>
       </c>
       <c r="G367" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H367" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="I367" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="J367" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="K367" t="s">
         <v>53</v>
       </c>
       <c r="L367" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="M367"/>
       <c r="N367" t="s">
@@ -23802,10 +23810,10 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="C368" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="D368" t="s">
         <v>18</v>
@@ -23817,22 +23825,22 @@
         <v>20</v>
       </c>
       <c r="G368" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H368" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="I368" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="J368" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="K368" t="s">
         <v>59</v>
       </c>
       <c r="L368" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="M368"/>
       <c r="N368" t="s">
@@ -23848,10 +23856,10 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C369" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D369" t="s">
         <v>18</v>
@@ -23863,22 +23871,22 @@
         <v>20</v>
       </c>
       <c r="G369" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H369" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="I369" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="J369" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="K369" t="s">
         <v>53</v>
       </c>
       <c r="L369" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="M369"/>
       <c r="N369" t="s">
@@ -23894,10 +23902,10 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="C370" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="D370" t="s">
         <v>18</v>
@@ -23909,22 +23917,22 @@
         <v>31</v>
       </c>
       <c r="G370" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H370" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="I370" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="J370" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="K370" t="s">
         <v>806</v>
       </c>
       <c r="L370" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="M370"/>
       <c r="N370" t="s">
@@ -23940,10 +23948,10 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="C371" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="D371" t="s">
         <v>18</v>
@@ -23955,7 +23963,7 @@
         <v>31</v>
       </c>
       <c r="G371" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H371" t="s">
         <v>980</v>
@@ -23964,13 +23972,13 @@
         <v>980</v>
       </c>
       <c r="J371" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="K371" t="s">
         <v>664</v>
       </c>
       <c r="L371" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="M371"/>
       <c r="N371" t="s">
@@ -23986,10 +23994,10 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="C372" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="D372" t="s">
         <v>18</v>
@@ -24001,22 +24009,22 @@
         <v>20</v>
       </c>
       <c r="G372" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H372" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="I372" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="J372" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="K372" t="s">
         <v>53</v>
       </c>
       <c r="L372" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="M372"/>
       <c r="N372" t="s">
@@ -24032,10 +24040,10 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="C373" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D373" t="s">
         <v>18</v>
@@ -24047,22 +24055,22 @@
         <v>263</v>
       </c>
       <c r="G373" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H373" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="I373" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="J373" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="K373" t="s">
         <v>24</v>
       </c>
       <c r="L373" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="M373"/>
       <c r="N373" t="s">
@@ -24078,10 +24086,10 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="C374" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="D374" t="s">
         <v>18</v>
@@ -24093,7 +24101,7 @@
         <v>20</v>
       </c>
       <c r="G374" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="H374" t="s">
         <v>220</v>
@@ -24102,13 +24110,13 @@
         <v>220</v>
       </c>
       <c r="J374" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="K374" t="s">
         <v>24</v>
       </c>
       <c r="L374" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="M374"/>
       <c r="N374" t="s">
@@ -24124,10 +24132,10 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="C375" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D375" t="s">
         <v>73</v>
@@ -24136,10 +24144,10 @@
         <v>19</v>
       </c>
       <c r="F375" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="G375" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H375" t="s">
         <v>698</v>
@@ -24148,13 +24156,13 @@
         <v>698</v>
       </c>
       <c r="J375" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="K375" t="s">
         <v>24</v>
       </c>
       <c r="L375" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="M375"/>
       <c r="N375" t="s">
@@ -24170,10 +24178,10 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C376" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D376" t="s">
         <v>18</v>
@@ -24185,22 +24193,22 @@
         <v>315</v>
       </c>
       <c r="G376" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H376" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="I376" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="J376" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="K376" t="s">
         <v>192</v>
       </c>
       <c r="L376" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="M376"/>
       <c r="N376" t="s">
@@ -24216,10 +24224,10 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C377" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="D377" t="s">
         <v>18</v>
@@ -24231,22 +24239,22 @@
         <v>155</v>
       </c>
       <c r="G377" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H377" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="I377" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="J377" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="K377" t="s">
         <v>53</v>
       </c>
       <c r="L377" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="M377"/>
       <c r="N377" t="s">
@@ -24262,10 +24270,10 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C378" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D378" t="s">
         <v>73</v>
@@ -24274,25 +24282,25 @@
         <v>19</v>
       </c>
       <c r="F378" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="G378" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H378" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I378" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J378" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="K378" t="s">
         <v>831</v>
       </c>
       <c r="L378" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="M378"/>
       <c r="N378" t="s">
@@ -24308,10 +24316,10 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C379" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D379" t="s">
         <v>18</v>
@@ -24320,25 +24328,25 @@
         <v>19</v>
       </c>
       <c r="F379" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G379" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H379" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="I379" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="J379" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K379" t="s">
         <v>24</v>
       </c>
       <c r="L379" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="M379"/>
       <c r="N379" t="s">
@@ -24354,10 +24362,10 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C380" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D380" t="s">
         <v>18</v>
@@ -24366,25 +24374,25 @@
         <v>19</v>
       </c>
       <c r="F380" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G380" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H380" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="I380" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="J380" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="K380" t="s">
         <v>53</v>
       </c>
       <c r="L380" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="M380"/>
       <c r="N380" t="s">
@@ -24400,10 +24408,10 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="C381" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="D381" t="s">
         <v>73</v>
@@ -24412,25 +24420,25 @@
         <v>19</v>
       </c>
       <c r="F381" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="G381" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H381" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="I381" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="J381" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="K381" t="s">
         <v>76</v>
       </c>
       <c r="L381" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="M381"/>
       <c r="N381" t="s">
@@ -24446,10 +24454,10 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="C382" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D382" t="s">
         <v>73</v>
@@ -24458,10 +24466,10 @@
         <v>19</v>
       </c>
       <c r="F382" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="G382" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H382" t="s">
         <v>817</v>
@@ -24470,13 +24478,13 @@
         <v>817</v>
       </c>
       <c r="J382" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="K382" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L382" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="M382"/>
       <c r="N382" t="s">
@@ -24492,10 +24500,10 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="C383" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="D383" t="s">
         <v>18</v>
@@ -24504,25 +24512,25 @@
         <v>19</v>
       </c>
       <c r="F383" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G383" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H383" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="I383" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="J383" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="K383" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="L383" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="M383"/>
       <c r="N383" t="s">
@@ -24538,10 +24546,10 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="C384" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="D384" t="s">
         <v>18</v>
@@ -24550,25 +24558,25 @@
         <v>19</v>
       </c>
       <c r="F384" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="G384" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H384" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="I384" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="J384" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="K384" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="L384" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="M384"/>
       <c r="N384" t="s">
@@ -24584,10 +24592,10 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="C385" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="D385" t="s">
         <v>18</v>
@@ -24599,22 +24607,22 @@
         <v>155</v>
       </c>
       <c r="G385" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H385" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="I385" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="J385" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="K385" t="s">
         <v>885</v>
       </c>
       <c r="L385" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="M385"/>
       <c r="N385" t="s">
@@ -24630,10 +24638,10 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C386" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="D386" t="s">
         <v>73</v>
@@ -24645,22 +24653,22 @@
         <v>155</v>
       </c>
       <c r="G386" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H386" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="I386" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="J386" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="K386" t="s">
         <v>664</v>
       </c>
       <c r="L386" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="M386"/>
       <c r="N386" t="s">
@@ -24676,10 +24684,10 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="C387" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="D387" t="s">
         <v>73</v>
@@ -24691,22 +24699,22 @@
         <v>673</v>
       </c>
       <c r="G387" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H387" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I387" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J387" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="K387" t="s">
         <v>286</v>
       </c>
       <c r="L387" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="M387"/>
       <c r="N387" t="s">
@@ -24722,10 +24730,10 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C388" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D388" t="s">
         <v>73</v>
@@ -24734,10 +24742,10 @@
         <v>19</v>
       </c>
       <c r="F388" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="G388" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H388" t="s">
         <v>949</v>
@@ -24746,13 +24754,13 @@
         <v>949</v>
       </c>
       <c r="J388" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="K388" t="s">
         <v>536</v>
       </c>
       <c r="L388" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="M388"/>
       <c r="N388" t="s">
@@ -24768,10 +24776,10 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="C389" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="D389" t="s">
         <v>73</v>
@@ -24780,25 +24788,25 @@
         <v>19</v>
       </c>
       <c r="F389" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G389" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H389" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I389" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J389" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="K389" t="s">
         <v>34</v>
       </c>
       <c r="L389" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="M389"/>
       <c r="N389" t="s">
@@ -24814,10 +24822,10 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="C390" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D390" t="s">
         <v>73</v>
@@ -24826,10 +24834,10 @@
         <v>19</v>
       </c>
       <c r="F390" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G390" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H390" t="s">
         <v>74</v>
@@ -24838,13 +24846,13 @@
         <v>74</v>
       </c>
       <c r="J390" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="K390" t="s">
         <v>34</v>
       </c>
       <c r="L390" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="M390"/>
       <c r="N390" t="s">
@@ -24860,10 +24868,10 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="C391" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="D391" t="s">
         <v>73</v>
@@ -24872,10 +24880,10 @@
         <v>19</v>
       </c>
       <c r="F391" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="G391" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H391" t="s">
         <v>829</v>
@@ -24884,13 +24892,13 @@
         <v>829</v>
       </c>
       <c r="J391" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="K391" t="s">
         <v>34</v>
       </c>
       <c r="L391" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="M391"/>
       <c r="N391" t="s">
@@ -24906,10 +24914,10 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="C392" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="D392" t="s">
         <v>73</v>
@@ -24918,10 +24926,10 @@
         <v>19</v>
       </c>
       <c r="F392" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="G392" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H392" t="s">
         <v>121</v>
@@ -24930,13 +24938,13 @@
         <v>121</v>
       </c>
       <c r="J392" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="K392" t="s">
         <v>34</v>
       </c>
       <c r="L392" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="M392"/>
       <c r="N392" t="s">
@@ -24952,10 +24960,10 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="C393" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="D393" t="s">
         <v>73</v>
@@ -24964,10 +24972,10 @@
         <v>19</v>
       </c>
       <c r="F393" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G393" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H393" t="s">
         <v>74</v>
@@ -24976,13 +24984,13 @@
         <v>74</v>
       </c>
       <c r="J393" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="K393" t="s">
         <v>76</v>
       </c>
       <c r="L393" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="M393"/>
       <c r="N393" t="s">
@@ -24998,10 +25006,10 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C394" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D394" t="s">
         <v>73</v>
@@ -25010,10 +25018,10 @@
         <v>19</v>
       </c>
       <c r="F394" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G394" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H394" t="s">
         <v>290</v>
@@ -25022,13 +25030,13 @@
         <v>290</v>
       </c>
       <c r="J394" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="K394" t="s">
         <v>53</v>
       </c>
       <c r="L394" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="M394"/>
       <c r="N394" t="s">
@@ -25044,10 +25052,10 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="C395" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="D395" t="s">
         <v>73</v>
@@ -25056,25 +25064,25 @@
         <v>19</v>
       </c>
       <c r="F395" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G395" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H395" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I395" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J395" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="K395" t="s">
         <v>382</v>
       </c>
       <c r="L395" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="M395"/>
       <c r="N395" t="s">
@@ -25090,10 +25098,10 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C396" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D396" t="s">
         <v>73</v>
@@ -25105,22 +25113,22 @@
         <v>315</v>
       </c>
       <c r="G396" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H396" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="I396" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="J396" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="K396" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="L396" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="M396"/>
       <c r="N396" t="s">
@@ -25136,10 +25144,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="C397" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D397" t="s">
         <v>73</v>
@@ -25148,10 +25156,10 @@
         <v>19</v>
       </c>
       <c r="F397" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G397" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H397" t="s">
         <v>1123</v>
@@ -25160,13 +25168,13 @@
         <v>1123</v>
       </c>
       <c r="J397" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="K397" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="L397" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="M397"/>
       <c r="N397" t="s">
@@ -25182,10 +25190,10 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C398" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D398" t="s">
         <v>73</v>
@@ -25194,25 +25202,25 @@
         <v>19</v>
       </c>
       <c r="F398" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G398" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H398" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I398" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J398" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="K398" t="s">
         <v>333</v>
       </c>
       <c r="L398" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="M398"/>
       <c r="N398" t="s">
@@ -25228,10 +25236,10 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C399" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D399" t="s">
         <v>73</v>
@@ -25243,22 +25251,22 @@
         <v>673</v>
       </c>
       <c r="G399" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H399" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I399" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J399" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="K399" t="s">
         <v>24</v>
       </c>
       <c r="L399" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="M399"/>
       <c r="N399" t="s">
@@ -25274,10 +25282,10 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="C400" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="D400" t="s">
         <v>73</v>
@@ -25286,10 +25294,10 @@
         <v>19</v>
       </c>
       <c r="F400" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="G400" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H400" t="s">
         <v>121</v>
@@ -25298,13 +25306,13 @@
         <v>121</v>
       </c>
       <c r="J400" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="K400" t="s">
         <v>24</v>
       </c>
       <c r="L400" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="M400"/>
       <c r="N400" t="s">
@@ -25320,40 +25328,40 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="C401" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="D401" t="s">
         <v>73</v>
       </c>
       <c r="E401" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="F401" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G401" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H401" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="I401" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="J401" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="K401" t="s">
         <v>426</v>
       </c>
       <c r="L401" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="M401" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="N401" t="s">
         <v>26</v>
@@ -25368,10 +25376,10 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="C402" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="D402" t="s">
         <v>73</v>
@@ -25380,25 +25388,25 @@
         <v>19</v>
       </c>
       <c r="F402" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G402" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H402" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="I402" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="J402" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K402" t="s">
         <v>53</v>
       </c>
       <c r="L402" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="M402"/>
       <c r="N402" t="s">
@@ -25414,10 +25422,10 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="C403" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="D403" t="s">
         <v>73</v>
@@ -25426,10 +25434,10 @@
         <v>19</v>
       </c>
       <c r="F403" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="G403" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H403" t="s">
         <v>698</v>
@@ -25438,13 +25446,13 @@
         <v>698</v>
       </c>
       <c r="J403" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K403" t="s">
         <v>53</v>
       </c>
       <c r="L403" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="M403"/>
       <c r="N403" t="s">
@@ -25460,10 +25468,10 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C404" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="D404" t="s">
         <v>73</v>
@@ -25472,25 +25480,25 @@
         <v>19</v>
       </c>
       <c r="F404" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="G404" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="H404" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="I404" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J404" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K404" t="s">
         <v>333</v>
       </c>
       <c r="L404" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="M404"/>
       <c r="N404" t="s">
@@ -25506,10 +25514,10 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="C405" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="D405" t="s">
         <v>18</v>
@@ -25518,25 +25526,25 @@
         <v>19</v>
       </c>
       <c r="F405" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="G405" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="H405" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="I405" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="J405" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K405" t="s">
         <v>24</v>
       </c>
       <c r="L405" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="M405"/>
       <c r="N405" t="s">
@@ -25552,10 +25560,10 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C406" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="D406" t="s">
         <v>18</v>
@@ -25564,25 +25572,25 @@
         <v>19</v>
       </c>
       <c r="F406" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="G406" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="H406" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="I406" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J406" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="K406" t="s">
         <v>53</v>
       </c>
       <c r="L406" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="M406"/>
       <c r="N406" t="s">
@@ -25598,10 +25606,10 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C407" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D407" t="s">
         <v>73</v>
@@ -25610,25 +25618,25 @@
         <v>19</v>
       </c>
       <c r="F407" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="G407" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="H407" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="I407" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="J407" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="K407" t="s">
         <v>53</v>
       </c>
       <c r="L407" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="M407"/>
       <c r="N407" t="s">
